--- a/Viajante/VIAJANTE.xlsx
+++ b/Viajante/VIAJANTE.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M2" t="n">
         <v>37.2</v>
@@ -633,7 +633,7 @@
         <v>4933.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>83.44</v>
+        <v>51.35</v>
       </c>
       <c r="T2" t="n">
-        <v>41.11</v>
+        <v>19.73</v>
       </c>
       <c r="U2" t="n">
-        <v>83.44</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="3">
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
@@ -702,7 +702,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -710,11 +710,11 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="4">
@@ -758,7 +758,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M4" t="n">
         <v>35.7</v>
@@ -773,7 +773,7 @@
         <v>10459.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>70.83</v>
+        <v>43.59</v>
       </c>
       <c r="T4" t="n">
-        <v>87.17</v>
+        <v>41.84</v>
       </c>
       <c r="U4" t="n">
-        <v>87.17</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="5">
@@ -831,7 +831,7 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
@@ -840,7 +840,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -848,11 +848,11 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>331.25</v>
+        <v>203.85</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>331.25</v>
+        <v>203.85</v>
       </c>
     </row>
     <row r="6">
@@ -896,7 +896,7 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
@@ -905,7 +905,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -913,11 +913,11 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>725</v>
+        <v>446.15</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>725</v>
+        <v>446.15</v>
       </c>
     </row>
     <row r="7">
@@ -961,7 +961,7 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M7" t="n">
         <v>37.8</v>
@@ -976,7 +976,7 @@
         <v>5191.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>75</v>
+        <v>46.15</v>
       </c>
       <c r="T7" t="n">
-        <v>43.26</v>
+        <v>20.77</v>
       </c>
       <c r="U7" t="n">
-        <v>75</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="8">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M8" t="n">
         <v>26.3</v>
@@ -1049,7 +1049,7 @@
         <v>4018.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>52.08</v>
+        <v>32.05</v>
       </c>
       <c r="T8" t="n">
-        <v>33.48</v>
+        <v>16.07</v>
       </c>
       <c r="U8" t="n">
-        <v>52.08</v>
+        <v>32.05</v>
       </c>
     </row>
     <row r="9">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M9" t="n">
         <v>84.09999999999999</v>
@@ -1122,7 +1122,7 @@
         <v>5451.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1130,13 +1130,13 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>166.67</v>
+        <v>102.56</v>
       </c>
       <c r="T9" t="n">
-        <v>45.43</v>
+        <v>21.8</v>
       </c>
       <c r="U9" t="n">
-        <v>166.67</v>
+        <v>102.56</v>
       </c>
     </row>
     <row r="10">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M10" t="n">
         <v>61</v>
@@ -1195,7 +1195,7 @@
         <v>6414.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1203,13 +1203,13 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>120.83</v>
+        <v>74.36</v>
       </c>
       <c r="T10" t="n">
-        <v>53.46</v>
+        <v>25.66</v>
       </c>
       <c r="U10" t="n">
-        <v>120.83</v>
+        <v>74.36</v>
       </c>
     </row>
     <row r="11">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M11" t="n">
         <v>31.5</v>
@@ -1268,7 +1268,7 @@
         <v>7507.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1276,13 +1276,13 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>62.5</v>
+        <v>38.46</v>
       </c>
       <c r="T11" t="n">
-        <v>62.56</v>
+        <v>30.03</v>
       </c>
       <c r="U11" t="n">
-        <v>62.56</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="12">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M12" t="n">
         <v>2.1</v>
@@ -1341,7 +1341,7 @@
         <v>366.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>4.17</v>
+        <v>2.56</v>
       </c>
       <c r="T12" t="n">
-        <v>3.05</v>
+        <v>1.46</v>
       </c>
       <c r="U12" t="n">
-        <v>4.17</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="13">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M13" t="n">
         <v>68.3</v>
@@ -1414,7 +1414,7 @@
         <v>17337.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1422,13 +1422,13 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>135.42</v>
+        <v>83.33</v>
       </c>
       <c r="T13" t="n">
-        <v>144.48</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>144.48</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="14">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M14" t="n">
         <v>4.2</v>
@@ -1487,7 +1487,7 @@
         <v>1246</v>
       </c>
       <c r="Q14" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>8.33</v>
+        <v>5.13</v>
       </c>
       <c r="T14" t="n">
-        <v>10.38</v>
+        <v>4.98</v>
       </c>
       <c r="U14" t="n">
-        <v>10.38</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="15">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M15" t="n">
         <v>52.1</v>
@@ -1560,7 +1560,7 @@
         <v>6908.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>116.88</v>
+        <v>71.92</v>
       </c>
       <c r="T15" t="n">
-        <v>57.57</v>
+        <v>27.63</v>
       </c>
       <c r="U15" t="n">
-        <v>116.88</v>
+        <v>71.92</v>
       </c>
     </row>
     <row r="16">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
@@ -1629,7 +1629,7 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -1637,11 +1637,11 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="17">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M17" t="n">
         <v>55.7</v>
@@ -1700,7 +1700,7 @@
         <v>16330.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -1708,13 +1708,13 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>110.42</v>
+        <v>67.95</v>
       </c>
       <c r="T17" t="n">
-        <v>136.08</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>136.08</v>
+        <v>67.95</v>
       </c>
     </row>
     <row r="18">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M18" t="n">
         <v>3.2</v>
@@ -1773,7 +1773,7 @@
         <v>473.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -1781,13 +1781,13 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>6.25</v>
+        <v>3.85</v>
       </c>
       <c r="T18" t="n">
-        <v>3.95</v>
+        <v>1.89</v>
       </c>
       <c r="U18" t="n">
-        <v>6.25</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="19">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
@@ -1840,7 +1840,7 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>543.75</v>
+        <v>334.62</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="n">
-        <v>543.75</v>
+        <v>334.62</v>
       </c>
     </row>
     <row r="20">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
@@ -1905,7 +1905,7 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>1156.25</v>
+        <v>711.54</v>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="n">
-        <v>1156.25</v>
+        <v>711.54</v>
       </c>
     </row>
     <row r="21">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M21" t="n">
         <v>55.7</v>
@@ -1976,7 +1976,7 @@
         <v>7664.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>110.42</v>
+        <v>67.95</v>
       </c>
       <c r="T21" t="n">
-        <v>63.87</v>
+        <v>30.66</v>
       </c>
       <c r="U21" t="n">
-        <v>110.42</v>
+        <v>67.95</v>
       </c>
     </row>
     <row r="22">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M22" t="n">
         <v>42</v>
@@ -2049,7 +2049,7 @@
         <v>6496.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>83.33</v>
+        <v>51.28</v>
       </c>
       <c r="T22" t="n">
-        <v>54.14</v>
+        <v>25.99</v>
       </c>
       <c r="U22" t="n">
-        <v>83.33</v>
+        <v>51.28</v>
       </c>
     </row>
     <row r="23">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M23" t="n">
         <v>113.5</v>
@@ -2122,7 +2122,7 @@
         <v>7359</v>
       </c>
       <c r="Q23" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -2130,13 +2130,13 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>225</v>
+        <v>138.46</v>
       </c>
       <c r="T23" t="n">
-        <v>61.32</v>
+        <v>29.44</v>
       </c>
       <c r="U23" t="n">
-        <v>225</v>
+        <v>138.46</v>
       </c>
     </row>
     <row r="24">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M24" t="n">
         <v>109.3</v>
@@ -2195,7 +2195,7 @@
         <v>11499.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -2203,13 +2203,13 @@
         </is>
       </c>
       <c r="S24" t="n">
-        <v>216.67</v>
+        <v>133.33</v>
       </c>
       <c r="T24" t="n">
-        <v>95.83</v>
+        <v>46</v>
       </c>
       <c r="U24" t="n">
-        <v>216.67</v>
+        <v>133.33</v>
       </c>
     </row>
     <row r="25">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M25" t="n">
         <v>49.4</v>
@@ -2268,7 +2268,7 @@
         <v>11914.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -2276,13 +2276,13 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>97.92</v>
+        <v>60.26</v>
       </c>
       <c r="T25" t="n">
-        <v>99.29000000000001</v>
+        <v>47.66</v>
       </c>
       <c r="U25" t="n">
-        <v>99.29000000000001</v>
+        <v>60.26</v>
       </c>
     </row>
     <row r="26">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M26" t="n">
         <v>1.1</v>
@@ -2341,7 +2341,7 @@
         <v>145.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -2349,13 +2349,13 @@
         </is>
       </c>
       <c r="S26" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
       <c r="T26" t="n">
-        <v>1.21</v>
+        <v>0.58</v>
       </c>
       <c r="U26" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="27">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M27" t="n">
         <v>108.3</v>
@@ -2414,7 +2414,7 @@
         <v>27708.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="S27" t="n">
-        <v>214.58</v>
+        <v>132.05</v>
       </c>
       <c r="T27" t="n">
-        <v>230.91</v>
+        <v>110.84</v>
       </c>
       <c r="U27" t="n">
-        <v>230.91</v>
+        <v>132.05</v>
       </c>
     </row>
     <row r="28">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M28" t="n">
         <v>5.3</v>
@@ -2487,7 +2487,7 @@
         <v>1441.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -2495,13 +2495,13 @@
         </is>
       </c>
       <c r="S28" t="n">
-        <v>10.42</v>
+        <v>6.41</v>
       </c>
       <c r="T28" t="n">
-        <v>12.01</v>
+        <v>5.77</v>
       </c>
       <c r="U28" t="n">
-        <v>12.01</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="29">
@@ -2531,14 +2531,14 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -2576,14 +2576,14 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M31" t="n">
         <v>35</v>
@@ -2650,7 +2650,7 @@
         <v>4643.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="S31" t="n">
-        <v>78.59</v>
+        <v>48.37</v>
       </c>
       <c r="T31" t="n">
-        <v>38.69</v>
+        <v>18.57</v>
       </c>
       <c r="U31" t="n">
-        <v>78.59</v>
+        <v>48.37</v>
       </c>
     </row>
     <row r="32">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
@@ -2719,7 +2719,7 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -2727,11 +2727,11 @@
         </is>
       </c>
       <c r="S32" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="33">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M33" t="n">
         <v>37.8</v>
@@ -2790,7 +2790,7 @@
         <v>10904.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -2798,13 +2798,13 @@
         </is>
       </c>
       <c r="S33" t="n">
-        <v>75</v>
+        <v>46.15</v>
       </c>
       <c r="T33" t="n">
-        <v>90.87</v>
+        <v>43.62</v>
       </c>
       <c r="U33" t="n">
-        <v>90.87</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="34">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M34" t="n">
         <v>25.2</v>
@@ -2863,7 +2863,7 @@
         <v>4593.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -2871,13 +2871,13 @@
         </is>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>30.77</v>
       </c>
       <c r="T34" t="n">
-        <v>38.28</v>
+        <v>18.37</v>
       </c>
       <c r="U34" t="n">
-        <v>50</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="35">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
@@ -2930,7 +2930,7 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -2938,11 +2938,11 @@
         </is>
       </c>
       <c r="S35" t="n">
-        <v>443.75</v>
+        <v>273.08</v>
       </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="n">
-        <v>443.75</v>
+        <v>273.08</v>
       </c>
     </row>
     <row r="36">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
@@ -2995,7 +2995,7 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -3003,11 +3003,11 @@
         </is>
       </c>
       <c r="S36" t="n">
-        <v>725</v>
+        <v>446.15</v>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="n">
-        <v>725</v>
+        <v>446.15</v>
       </c>
     </row>
     <row r="37">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M37" t="n">
         <v>12.6</v>
@@ -3066,7 +3066,7 @@
         <v>1705.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>15.38</v>
       </c>
       <c r="T37" t="n">
-        <v>14.21</v>
+        <v>6.82</v>
       </c>
       <c r="U37" t="n">
-        <v>25</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="38">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M38" t="n">
         <v>29.4</v>
@@ -3139,7 +3139,7 @@
         <v>4535</v>
       </c>
       <c r="Q38" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -3147,13 +3147,13 @@
         </is>
       </c>
       <c r="S38" t="n">
-        <v>58.33</v>
+        <v>35.9</v>
       </c>
       <c r="T38" t="n">
-        <v>37.79</v>
+        <v>18.14</v>
       </c>
       <c r="U38" t="n">
-        <v>58.33</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="39">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M39" t="n">
         <v>22.1</v>
@@ -3212,7 +3212,7 @@
         <v>1430.9</v>
       </c>
       <c r="Q39" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -3220,13 +3220,13 @@
         </is>
       </c>
       <c r="S39" t="n">
-        <v>43.75</v>
+        <v>26.92</v>
       </c>
       <c r="T39" t="n">
-        <v>11.92</v>
+        <v>5.72</v>
       </c>
       <c r="U39" t="n">
-        <v>43.75</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="40">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M40" t="n">
         <v>72.5</v>
@@ -3285,7 +3285,7 @@
         <v>7646.7</v>
       </c>
       <c r="Q40" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -3293,13 +3293,13 @@
         </is>
       </c>
       <c r="S40" t="n">
-        <v>143.75</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="T40" t="n">
-        <v>63.72</v>
+        <v>30.59</v>
       </c>
       <c r="U40" t="n">
-        <v>143.75</v>
+        <v>88.45999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M41" t="n">
         <v>24.2</v>
@@ -3358,7 +3358,7 @@
         <v>5705.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="S41" t="n">
-        <v>47.92</v>
+        <v>29.49</v>
       </c>
       <c r="T41" t="n">
-        <v>47.55</v>
+        <v>22.82</v>
       </c>
       <c r="U41" t="n">
-        <v>47.92</v>
+        <v>29.49</v>
       </c>
     </row>
     <row r="42">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M42" t="n">
         <v>67.3</v>
@@ -3431,7 +3431,7 @@
         <v>17234.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -3439,13 +3439,13 @@
         </is>
       </c>
       <c r="S42" t="n">
-        <v>133.33</v>
+        <v>82.05</v>
       </c>
       <c r="T42" t="n">
-        <v>143.62</v>
+        <v>68.94</v>
       </c>
       <c r="U42" t="n">
-        <v>143.62</v>
+        <v>82.05</v>
       </c>
     </row>
     <row r="43">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M43" t="n">
         <v>1.1</v>
@@ -3504,7 +3504,7 @@
         <v>100.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -3512,13 +3512,13 @@
         </is>
       </c>
       <c r="S43" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
       <c r="T43" t="n">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="U43" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="44">
@@ -3548,14 +3548,14 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -3593,14 +3593,14 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -3638,14 +3638,14 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -3683,14 +3683,14 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M48" t="n">
         <v>32.7</v>
@@ -3757,7 +3757,7 @@
         <v>4339.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="S48" t="n">
-        <v>73.44</v>
+        <v>45.19</v>
       </c>
       <c r="T48" t="n">
-        <v>36.16</v>
+        <v>17.36</v>
       </c>
       <c r="U48" t="n">
-        <v>73.44</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="49">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
@@ -3826,7 +3826,7 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -3834,11 +3834,11 @@
         </is>
       </c>
       <c r="S49" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="50">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M50" t="n">
         <v>30.5</v>
@@ -3897,7 +3897,7 @@
         <v>8962.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="S50" t="n">
-        <v>60.42</v>
+        <v>37.18</v>
       </c>
       <c r="T50" t="n">
-        <v>74.69</v>
+        <v>35.85</v>
       </c>
       <c r="U50" t="n">
-        <v>74.69</v>
+        <v>37.18</v>
       </c>
     </row>
     <row r="51">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
@@ -3964,7 +3964,7 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -3972,11 +3972,11 @@
         </is>
       </c>
       <c r="S51" t="n">
-        <v>287.5</v>
+        <v>176.92</v>
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="n">
-        <v>287.5</v>
+        <v>176.92</v>
       </c>
     </row>
     <row r="52">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
@@ -4029,7 +4029,7 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -4037,11 +4037,11 @@
         </is>
       </c>
       <c r="S52" t="n">
-        <v>600</v>
+        <v>369.23</v>
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="n">
-        <v>600</v>
+        <v>369.23</v>
       </c>
     </row>
     <row r="53">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M53" t="n">
         <v>32.6</v>
@@ -4100,7 +4100,7 @@
         <v>4477.5</v>
       </c>
       <c r="Q53" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -4108,13 +4108,13 @@
         </is>
       </c>
       <c r="S53" t="n">
-        <v>64.58</v>
+        <v>39.74</v>
       </c>
       <c r="T53" t="n">
-        <v>37.31</v>
+        <v>17.91</v>
       </c>
       <c r="U53" t="n">
-        <v>64.58</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="54">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M54" t="n">
         <v>22.1</v>
@@ -4173,7 +4173,7 @@
         <v>3358.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -4181,13 +4181,13 @@
         </is>
       </c>
       <c r="S54" t="n">
-        <v>43.75</v>
+        <v>26.92</v>
       </c>
       <c r="T54" t="n">
-        <v>27.98</v>
+        <v>13.43</v>
       </c>
       <c r="U54" t="n">
-        <v>43.75</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="55">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M55" t="n">
         <v>67.3</v>
@@ -4246,7 +4246,7 @@
         <v>4361</v>
       </c>
       <c r="Q55" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -4254,13 +4254,13 @@
         </is>
       </c>
       <c r="S55" t="n">
-        <v>133.33</v>
+        <v>82.05</v>
       </c>
       <c r="T55" t="n">
-        <v>36.34</v>
+        <v>17.44</v>
       </c>
       <c r="U55" t="n">
-        <v>133.33</v>
+        <v>82.05</v>
       </c>
     </row>
     <row r="56">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M56" t="n">
         <v>55.7</v>
@@ -4319,7 +4319,7 @@
         <v>5855.9</v>
       </c>
       <c r="Q56" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -4327,13 +4327,13 @@
         </is>
       </c>
       <c r="S56" t="n">
-        <v>110.42</v>
+        <v>67.95</v>
       </c>
       <c r="T56" t="n">
-        <v>48.8</v>
+        <v>23.42</v>
       </c>
       <c r="U56" t="n">
-        <v>110.42</v>
+        <v>67.95</v>
       </c>
     </row>
     <row r="57">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M57" t="n">
         <v>27.3</v>
@@ -4392,7 +4392,7 @@
         <v>6518.7</v>
       </c>
       <c r="Q57" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -4400,13 +4400,13 @@
         </is>
       </c>
       <c r="S57" t="n">
-        <v>54.17</v>
+        <v>33.33</v>
       </c>
       <c r="T57" t="n">
-        <v>54.32</v>
+        <v>26.07</v>
       </c>
       <c r="U57" t="n">
-        <v>54.32</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="58">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M58" t="n">
         <v>1.1</v>
@@ -4465,7 +4465,7 @@
         <v>74.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="S58" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
       <c r="T58" t="n">
-        <v>0.62</v>
+        <v>0.3</v>
       </c>
       <c r="U58" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="59">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M59" t="n">
         <v>56.8</v>
@@ -4538,7 +4538,7 @@
         <v>14392.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -4546,13 +4546,13 @@
         </is>
       </c>
       <c r="S59" t="n">
-        <v>112.5</v>
+        <v>69.23</v>
       </c>
       <c r="T59" t="n">
-        <v>119.94</v>
+        <v>57.57</v>
       </c>
       <c r="U59" t="n">
-        <v>119.94</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="60">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M60" t="n">
         <v>3.2</v>
@@ -4611,7 +4611,7 @@
         <v>740.7</v>
       </c>
       <c r="Q60" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -4619,13 +4619,13 @@
         </is>
       </c>
       <c r="S60" t="n">
-        <v>6.25</v>
+        <v>3.85</v>
       </c>
       <c r="T60" t="n">
-        <v>6.17</v>
+        <v>2.96</v>
       </c>
       <c r="U60" t="n">
-        <v>6.25</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="61">
@@ -4655,14 +4655,14 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -4700,14 +4700,14 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M63" t="n">
         <v>38.6</v>
@@ -4774,7 +4774,7 @@
         <v>5116</v>
       </c>
       <c r="Q63" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="S63" t="n">
-        <v>86.56</v>
+        <v>53.27</v>
       </c>
       <c r="T63" t="n">
-        <v>42.63</v>
+        <v>20.46</v>
       </c>
       <c r="U63" t="n">
-        <v>86.56</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="64">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="n">
@@ -4843,7 +4843,7 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
@@ -4851,11 +4851,11 @@
         </is>
       </c>
       <c r="S64" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="65">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M65" t="n">
         <v>48.3</v>
@@ -4914,7 +4914,7 @@
         <v>14062.1</v>
       </c>
       <c r="Q65" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
@@ -4922,13 +4922,13 @@
         </is>
       </c>
       <c r="S65" t="n">
-        <v>95.83</v>
+        <v>58.97</v>
       </c>
       <c r="T65" t="n">
-        <v>117.18</v>
+        <v>56.25</v>
       </c>
       <c r="U65" t="n">
-        <v>117.18</v>
+        <v>58.97</v>
       </c>
     </row>
     <row r="66">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M66" t="n">
         <v>29.4</v>
@@ -4987,7 +4987,7 @@
         <v>5397.2</v>
       </c>
       <c r="Q66" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -4995,13 +4995,13 @@
         </is>
       </c>
       <c r="S66" t="n">
-        <v>58.33</v>
+        <v>35.9</v>
       </c>
       <c r="T66" t="n">
-        <v>44.98</v>
+        <v>21.59</v>
       </c>
       <c r="U66" t="n">
-        <v>58.33</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="67">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
@@ -5054,7 +5054,7 @@
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
@@ -5062,11 +5062,11 @@
         </is>
       </c>
       <c r="S67" t="n">
-        <v>537.5</v>
+        <v>330.77</v>
       </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="n">
-        <v>537.5</v>
+        <v>330.77</v>
       </c>
     </row>
     <row r="68">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="n">
@@ -5119,7 +5119,7 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -5127,11 +5127,11 @@
         </is>
       </c>
       <c r="S68" t="n">
-        <v>668.75</v>
+        <v>411.54</v>
       </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="n">
-        <v>668.75</v>
+        <v>411.54</v>
       </c>
     </row>
     <row r="69">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M69" t="n">
         <v>15.8</v>
@@ -5190,7 +5190,7 @@
         <v>2129.6</v>
       </c>
       <c r="Q69" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -5198,13 +5198,13 @@
         </is>
       </c>
       <c r="S69" t="n">
-        <v>31.25</v>
+        <v>19.23</v>
       </c>
       <c r="T69" t="n">
-        <v>17.75</v>
+        <v>8.52</v>
       </c>
       <c r="U69" t="n">
-        <v>31.25</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="70">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M70" t="n">
         <v>24.2</v>
@@ -5263,7 +5263,7 @@
         <v>3755.8</v>
       </c>
       <c r="Q70" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -5271,13 +5271,13 @@
         </is>
       </c>
       <c r="S70" t="n">
-        <v>47.92</v>
+        <v>29.49</v>
       </c>
       <c r="T70" t="n">
-        <v>31.3</v>
+        <v>15.02</v>
       </c>
       <c r="U70" t="n">
-        <v>47.92</v>
+        <v>29.49</v>
       </c>
     </row>
     <row r="71">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M71" t="n">
         <v>90.40000000000001</v>
@@ -5336,7 +5336,7 @@
         <v>9507.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -5344,13 +5344,13 @@
         </is>
       </c>
       <c r="S71" t="n">
-        <v>179.17</v>
+        <v>110.26</v>
       </c>
       <c r="T71" t="n">
-        <v>79.23</v>
+        <v>38.03</v>
       </c>
       <c r="U71" t="n">
-        <v>179.17</v>
+        <v>110.26</v>
       </c>
     </row>
     <row r="72">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M72" t="n">
         <v>29.4</v>
@@ -5409,7 +5409,7 @@
         <v>7040.6</v>
       </c>
       <c r="Q72" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
@@ -5417,13 +5417,13 @@
         </is>
       </c>
       <c r="S72" t="n">
-        <v>58.33</v>
+        <v>35.9</v>
       </c>
       <c r="T72" t="n">
-        <v>58.67</v>
+        <v>28.16</v>
       </c>
       <c r="U72" t="n">
-        <v>58.67</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="73">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M73" t="n">
         <v>63.1</v>
@@ -5482,7 +5482,7 @@
         <v>16059</v>
       </c>
       <c r="Q73" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
@@ -5490,13 +5490,13 @@
         </is>
       </c>
       <c r="S73" t="n">
-        <v>125</v>
+        <v>76.92</v>
       </c>
       <c r="T73" t="n">
-        <v>133.82</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="U73" t="n">
-        <v>133.82</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="74">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M74" t="n">
         <v>4.2</v>
@@ -5555,7 +5555,7 @@
         <v>1194.9</v>
       </c>
       <c r="Q74" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
@@ -5563,13 +5563,13 @@
         </is>
       </c>
       <c r="S74" t="n">
-        <v>8.33</v>
+        <v>5.13</v>
       </c>
       <c r="T74" t="n">
-        <v>9.960000000000001</v>
+        <v>4.78</v>
       </c>
       <c r="U74" t="n">
-        <v>9.960000000000001</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="75">
@@ -5599,14 +5599,14 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -5644,14 +5644,14 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -5689,14 +5689,14 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -5734,14 +5734,14 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M79" t="n">
         <v>42.8</v>
@@ -5808,7 +5808,7 @@
         <v>5679.1</v>
       </c>
       <c r="Q79" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -5816,13 +5816,13 @@
         </is>
       </c>
       <c r="S79" t="n">
-        <v>96.09</v>
+        <v>59.13</v>
       </c>
       <c r="T79" t="n">
-        <v>47.33</v>
+        <v>22.72</v>
       </c>
       <c r="U79" t="n">
-        <v>96.09</v>
+        <v>59.13</v>
       </c>
     </row>
     <row r="80">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="n">
@@ -5877,7 +5877,7 @@
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
@@ -5885,11 +5885,11 @@
         </is>
       </c>
       <c r="S80" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="81">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M81" t="n">
         <v>45.2</v>
@@ -5948,7 +5948,7 @@
         <v>13212.2</v>
       </c>
       <c r="Q81" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
@@ -5956,13 +5956,13 @@
         </is>
       </c>
       <c r="S81" t="n">
-        <v>89.58</v>
+        <v>55.13</v>
       </c>
       <c r="T81" t="n">
-        <v>110.1</v>
+        <v>52.85</v>
       </c>
       <c r="U81" t="n">
-        <v>110.1</v>
+        <v>55.13</v>
       </c>
     </row>
     <row r="82">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M82" t="n">
         <v>1.1</v>
@@ -6021,7 +6021,7 @@
         <v>142</v>
       </c>
       <c r="Q82" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
@@ -6029,13 +6029,13 @@
         </is>
       </c>
       <c r="S82" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
       <c r="T82" t="n">
-        <v>1.18</v>
+        <v>0.57</v>
       </c>
       <c r="U82" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="83">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="n">
@@ -6088,7 +6088,7 @@
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
@@ -6096,11 +6096,11 @@
         </is>
       </c>
       <c r="S83" t="n">
-        <v>343.75</v>
+        <v>211.54</v>
       </c>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="n">
-        <v>343.75</v>
+        <v>211.54</v>
       </c>
     </row>
     <row r="84">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="n">
@@ -6153,7 +6153,7 @@
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
@@ -6161,11 +6161,11 @@
         </is>
       </c>
       <c r="S84" t="n">
-        <v>762.5</v>
+        <v>469.23</v>
       </c>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="n">
-        <v>762.5</v>
+        <v>469.23</v>
       </c>
     </row>
     <row r="85">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M85" t="n">
         <v>44.1</v>
@@ -6224,7 +6224,7 @@
         <v>6034.8</v>
       </c>
       <c r="Q85" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
@@ -6232,13 +6232,13 @@
         </is>
       </c>
       <c r="S85" t="n">
-        <v>87.5</v>
+        <v>53.85</v>
       </c>
       <c r="T85" t="n">
-        <v>50.29</v>
+        <v>24.14</v>
       </c>
       <c r="U85" t="n">
-        <v>87.5</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="86">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M86" t="n">
         <v>27.3</v>
@@ -6297,7 +6297,7 @@
         <v>4217</v>
       </c>
       <c r="Q86" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
@@ -6305,13 +6305,13 @@
         </is>
       </c>
       <c r="S86" t="n">
-        <v>54.17</v>
+        <v>33.33</v>
       </c>
       <c r="T86" t="n">
-        <v>35.14</v>
+        <v>16.87</v>
       </c>
       <c r="U86" t="n">
-        <v>54.17</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="87">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M87" t="n">
         <v>85.09999999999999</v>
@@ -6370,7 +6370,7 @@
         <v>5519.2</v>
       </c>
       <c r="Q87" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
@@ -6378,13 +6378,13 @@
         </is>
       </c>
       <c r="S87" t="n">
-        <v>168.75</v>
+        <v>103.85</v>
       </c>
       <c r="T87" t="n">
-        <v>45.99</v>
+        <v>22.08</v>
       </c>
       <c r="U87" t="n">
-        <v>168.75</v>
+        <v>103.85</v>
       </c>
     </row>
     <row r="88">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M88" t="n">
         <v>76.7</v>
@@ -6443,7 +6443,7 @@
         <v>8082.1</v>
       </c>
       <c r="Q88" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
@@ -6451,13 +6451,13 @@
         </is>
       </c>
       <c r="S88" t="n">
-        <v>152.08</v>
+        <v>93.59</v>
       </c>
       <c r="T88" t="n">
-        <v>67.34999999999999</v>
+        <v>32.33</v>
       </c>
       <c r="U88" t="n">
-        <v>152.08</v>
+        <v>93.59</v>
       </c>
     </row>
     <row r="89">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M89" t="n">
         <v>31.5</v>
@@ -6516,7 +6516,7 @@
         <v>7610.8</v>
       </c>
       <c r="Q89" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
@@ -6524,13 +6524,13 @@
         </is>
       </c>
       <c r="S89" t="n">
-        <v>62.5</v>
+        <v>38.46</v>
       </c>
       <c r="T89" t="n">
-        <v>63.42</v>
+        <v>30.44</v>
       </c>
       <c r="U89" t="n">
-        <v>63.42</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="90">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M90" t="n">
         <v>1.1</v>
@@ -6589,7 +6589,7 @@
         <v>138</v>
       </c>
       <c r="Q90" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
@@ -6597,13 +6597,13 @@
         </is>
       </c>
       <c r="S90" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
       <c r="T90" t="n">
-        <v>1.15</v>
+        <v>0.55</v>
       </c>
       <c r="U90" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="91">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M91" t="n">
         <v>71.5</v>
@@ -6662,7 +6662,7 @@
         <v>18279.6</v>
       </c>
       <c r="Q91" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="S91" t="n">
-        <v>141.67</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="T91" t="n">
-        <v>152.33</v>
+        <v>73.12</v>
       </c>
       <c r="U91" t="n">
-        <v>152.33</v>
+        <v>87.18000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M92" t="n">
         <v>5.3</v>
@@ -6735,7 +6735,7 @@
         <v>1477.4</v>
       </c>
       <c r="Q92" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
@@ -6743,13 +6743,13 @@
         </is>
       </c>
       <c r="S92" t="n">
-        <v>10.42</v>
+        <v>6.41</v>
       </c>
       <c r="T92" t="n">
-        <v>12.31</v>
+        <v>5.91</v>
       </c>
       <c r="U92" t="n">
-        <v>12.31</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="93">
@@ -6779,14 +6779,14 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
@@ -6824,14 +6824,14 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M95" t="n">
         <v>39</v>
@@ -6898,7 +6898,7 @@
         <v>5169.8</v>
       </c>
       <c r="Q95" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
@@ -6906,13 +6906,13 @@
         </is>
       </c>
       <c r="S95" t="n">
-        <v>87.5</v>
+        <v>53.85</v>
       </c>
       <c r="T95" t="n">
-        <v>43.08</v>
+        <v>20.68</v>
       </c>
       <c r="U95" t="n">
-        <v>87.5</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="96">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="n">
@@ -6967,7 +6967,7 @@
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
@@ -6975,11 +6975,11 @@
         </is>
       </c>
       <c r="S96" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="97">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M97" t="n">
         <v>38.9</v>
@@ -7038,7 +7038,7 @@
         <v>11354.1</v>
       </c>
       <c r="Q97" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
@@ -7046,13 +7046,13 @@
         </is>
       </c>
       <c r="S97" t="n">
-        <v>77.08</v>
+        <v>47.44</v>
       </c>
       <c r="T97" t="n">
-        <v>94.62</v>
+        <v>45.42</v>
       </c>
       <c r="U97" t="n">
-        <v>94.62</v>
+        <v>47.44</v>
       </c>
     </row>
     <row r="98">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M98" t="n">
         <v>1.1</v>
@@ -7111,7 +7111,7 @@
         <v>71.40000000000001</v>
       </c>
       <c r="Q98" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="S98" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
       <c r="T98" t="n">
-        <v>0.6</v>
+        <v>0.29</v>
       </c>
       <c r="U98" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="99">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="n">
@@ -7178,7 +7178,7 @@
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
@@ -7186,11 +7186,11 @@
         </is>
       </c>
       <c r="S99" t="n">
-        <v>362.5</v>
+        <v>223.08</v>
       </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="n">
-        <v>362.5</v>
+        <v>223.08</v>
       </c>
     </row>
     <row r="100">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="n">
@@ -7243,7 +7243,7 @@
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
@@ -7251,11 +7251,11 @@
         </is>
       </c>
       <c r="S100" t="n">
-        <v>800</v>
+        <v>492.31</v>
       </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="n">
-        <v>800</v>
+        <v>492.31</v>
       </c>
     </row>
     <row r="101">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M101" t="n">
         <v>39.9</v>
@@ -7314,7 +7314,7 @@
         <v>5479.1</v>
       </c>
       <c r="Q101" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
@@ -7322,13 +7322,13 @@
         </is>
       </c>
       <c r="S101" t="n">
-        <v>79.17</v>
+        <v>48.72</v>
       </c>
       <c r="T101" t="n">
-        <v>45.66</v>
+        <v>21.92</v>
       </c>
       <c r="U101" t="n">
-        <v>79.17</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="102">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M102" t="n">
         <v>31.5</v>
@@ -7387,7 +7387,7 @@
         <v>4806.9</v>
       </c>
       <c r="Q102" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
@@ -7395,13 +7395,13 @@
         </is>
       </c>
       <c r="S102" t="n">
-        <v>62.5</v>
+        <v>38.46</v>
       </c>
       <c r="T102" t="n">
-        <v>40.06</v>
+        <v>19.23</v>
       </c>
       <c r="U102" t="n">
-        <v>62.5</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="103">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M103" t="n">
         <v>91.40000000000001</v>
@@ -7460,7 +7460,7 @@
         <v>5928.1</v>
       </c>
       <c r="Q103" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
@@ -7468,13 +7468,13 @@
         </is>
       </c>
       <c r="S103" t="n">
-        <v>181.25</v>
+        <v>111.54</v>
       </c>
       <c r="T103" t="n">
-        <v>49.4</v>
+        <v>23.71</v>
       </c>
       <c r="U103" t="n">
-        <v>181.25</v>
+        <v>111.54</v>
       </c>
     </row>
     <row r="104">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M104" t="n">
         <v>69.40000000000001</v>
@@ -7533,7 +7533,7 @@
         <v>7299.2</v>
       </c>
       <c r="Q104" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
@@ -7541,13 +7541,13 @@
         </is>
       </c>
       <c r="S104" t="n">
-        <v>137.5</v>
+        <v>84.62</v>
       </c>
       <c r="T104" t="n">
-        <v>60.83</v>
+        <v>29.2</v>
       </c>
       <c r="U104" t="n">
-        <v>137.5</v>
+        <v>84.62</v>
       </c>
     </row>
     <row r="105">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M105" t="n">
         <v>34.7</v>
@@ -7606,7 +7606,7 @@
         <v>8259.4</v>
       </c>
       <c r="Q105" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
@@ -7614,13 +7614,13 @@
         </is>
       </c>
       <c r="S105" t="n">
-        <v>68.75</v>
+        <v>42.31</v>
       </c>
       <c r="T105" t="n">
-        <v>68.83</v>
+        <v>33.04</v>
       </c>
       <c r="U105" t="n">
-        <v>68.83</v>
+        <v>42.31</v>
       </c>
     </row>
     <row r="106">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M106" t="n">
         <v>1.1</v>
@@ -7679,7 +7679,7 @@
         <v>135.8</v>
       </c>
       <c r="Q106" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R106" t="inlineStr">
         <is>
@@ -7687,13 +7687,13 @@
         </is>
       </c>
       <c r="S106" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
       <c r="T106" t="n">
-        <v>1.13</v>
+        <v>0.54</v>
       </c>
       <c r="U106" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="107">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M107" t="n">
         <v>74.59999999999999</v>
@@ -7752,7 +7752,7 @@
         <v>19133.2</v>
       </c>
       <c r="Q107" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R107" t="inlineStr">
         <is>
@@ -7760,13 +7760,13 @@
         </is>
       </c>
       <c r="S107" t="n">
-        <v>147.92</v>
+        <v>91.03</v>
       </c>
       <c r="T107" t="n">
-        <v>159.44</v>
+        <v>76.53</v>
       </c>
       <c r="U107" t="n">
-        <v>159.44</v>
+        <v>91.03</v>
       </c>
     </row>
     <row r="108">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M108" t="n">
         <v>3.2</v>
@@ -7825,7 +7825,7 @@
         <v>764.3</v>
       </c>
       <c r="Q108" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R108" t="inlineStr">
         <is>
@@ -7833,13 +7833,13 @@
         </is>
       </c>
       <c r="S108" t="n">
-        <v>6.25</v>
+        <v>3.85</v>
       </c>
       <c r="T108" t="n">
-        <v>6.37</v>
+        <v>3.06</v>
       </c>
       <c r="U108" t="n">
-        <v>6.37</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="109">
@@ -7869,14 +7869,14 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R109" t="inlineStr">
         <is>
@@ -7914,14 +7914,14 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R110" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M111" t="n">
         <v>47</v>
@@ -7988,7 +7988,7 @@
         <v>6244.6</v>
       </c>
       <c r="Q111" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R111" t="inlineStr">
         <is>
@@ -7996,13 +7996,13 @@
         </is>
       </c>
       <c r="S111" t="n">
-        <v>105.62</v>
+        <v>65</v>
       </c>
       <c r="T111" t="n">
-        <v>52.04</v>
+        <v>24.98</v>
       </c>
       <c r="U111" t="n">
-        <v>105.62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="112">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="n">
@@ -8057,7 +8057,7 @@
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R112" t="inlineStr">
         <is>
@@ -8065,11 +8065,11 @@
         </is>
       </c>
       <c r="S112" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="113">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M113" t="n">
         <v>49.4</v>
@@ -8128,7 +8128,7 @@
         <v>14337</v>
       </c>
       <c r="Q113" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R113" t="inlineStr">
         <is>
@@ -8136,13 +8136,13 @@
         </is>
       </c>
       <c r="S113" t="n">
-        <v>97.92</v>
+        <v>60.26</v>
       </c>
       <c r="T113" t="n">
-        <v>119.48</v>
+        <v>57.35</v>
       </c>
       <c r="U113" t="n">
-        <v>119.48</v>
+        <v>60.26</v>
       </c>
     </row>
     <row r="114">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="n">
@@ -8195,7 +8195,7 @@
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R114" t="inlineStr">
         <is>
@@ -8203,11 +8203,11 @@
         </is>
       </c>
       <c r="S114" t="n">
-        <v>487.5</v>
+        <v>300</v>
       </c>
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="n">
-        <v>487.5</v>
+        <v>300</v>
       </c>
     </row>
     <row r="115">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="n">
@@ -8260,7 +8260,7 @@
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R115" t="inlineStr">
         <is>
@@ -8268,11 +8268,11 @@
         </is>
       </c>
       <c r="S115" t="n">
-        <v>1031.25</v>
+        <v>634.62</v>
       </c>
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="n">
-        <v>1031.25</v>
+        <v>634.62</v>
       </c>
     </row>
     <row r="116">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M116" t="n">
         <v>53.6</v>
@@ -8331,7 +8331,7 @@
         <v>7347.9</v>
       </c>
       <c r="Q116" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R116" t="inlineStr">
         <is>
@@ -8339,13 +8339,13 @@
         </is>
       </c>
       <c r="S116" t="n">
-        <v>106.25</v>
+        <v>65.38</v>
       </c>
       <c r="T116" t="n">
-        <v>61.23</v>
+        <v>29.39</v>
       </c>
       <c r="U116" t="n">
-        <v>106.25</v>
+        <v>65.38</v>
       </c>
     </row>
     <row r="117">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M117" t="n">
         <v>36.8</v>
@@ -8404,7 +8404,7 @@
         <v>5633</v>
       </c>
       <c r="Q117" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R117" t="inlineStr">
         <is>
@@ -8412,13 +8412,13 @@
         </is>
       </c>
       <c r="S117" t="n">
-        <v>72.92</v>
+        <v>44.87</v>
       </c>
       <c r="T117" t="n">
-        <v>46.94</v>
+        <v>22.53</v>
       </c>
       <c r="U117" t="n">
-        <v>72.92</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="118">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M118" t="n">
         <v>113.5</v>
@@ -8477,7 +8477,7 @@
         <v>7359</v>
       </c>
       <c r="Q118" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R118" t="inlineStr">
         <is>
@@ -8485,13 +8485,13 @@
         </is>
       </c>
       <c r="S118" t="n">
-        <v>225</v>
+        <v>138.46</v>
       </c>
       <c r="T118" t="n">
-        <v>61.32</v>
+        <v>29.44</v>
       </c>
       <c r="U118" t="n">
-        <v>225</v>
+        <v>138.46</v>
       </c>
     </row>
     <row r="119">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M119" t="n">
         <v>90.40000000000001</v>
@@ -8550,7 +8550,7 @@
         <v>9521.5</v>
       </c>
       <c r="Q119" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R119" t="inlineStr">
         <is>
@@ -8558,13 +8558,13 @@
         </is>
       </c>
       <c r="S119" t="n">
-        <v>179.17</v>
+        <v>110.26</v>
       </c>
       <c r="T119" t="n">
-        <v>79.34999999999999</v>
+        <v>38.09</v>
       </c>
       <c r="U119" t="n">
-        <v>179.17</v>
+        <v>110.26</v>
       </c>
     </row>
     <row r="120">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M120" t="n">
         <v>46.2</v>
@@ -8623,7 +8623,7 @@
         <v>11089.4</v>
       </c>
       <c r="Q120" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R120" t="inlineStr">
         <is>
@@ -8631,13 +8631,13 @@
         </is>
       </c>
       <c r="S120" t="n">
-        <v>91.67</v>
+        <v>56.41</v>
       </c>
       <c r="T120" t="n">
-        <v>92.41</v>
+        <v>44.36</v>
       </c>
       <c r="U120" t="n">
-        <v>92.41</v>
+        <v>56.41</v>
       </c>
     </row>
     <row r="121">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M121" t="n">
         <v>96.7</v>
@@ -8696,7 +8696,7 @@
         <v>24723.1</v>
       </c>
       <c r="Q121" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R121" t="inlineStr">
         <is>
@@ -8704,13 +8704,13 @@
         </is>
       </c>
       <c r="S121" t="n">
-        <v>191.67</v>
+        <v>117.95</v>
       </c>
       <c r="T121" t="n">
-        <v>206.03</v>
+        <v>98.89</v>
       </c>
       <c r="U121" t="n">
-        <v>206.03</v>
+        <v>117.95</v>
       </c>
     </row>
     <row r="122">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M122" t="n">
         <v>4.2</v>
@@ -8769,7 +8769,7 @@
         <v>1230.4</v>
       </c>
       <c r="Q122" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R122" t="inlineStr">
         <is>
@@ -8777,13 +8777,13 @@
         </is>
       </c>
       <c r="S122" t="n">
-        <v>8.33</v>
+        <v>5.13</v>
       </c>
       <c r="T122" t="n">
-        <v>10.25</v>
+        <v>4.92</v>
       </c>
       <c r="U122" t="n">
-        <v>10.25</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="123">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M123" t="n">
         <v>54</v>
@@ -8842,7 +8842,7 @@
         <v>7166.9</v>
       </c>
       <c r="Q123" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R123" t="inlineStr">
         <is>
@@ -8850,13 +8850,13 @@
         </is>
       </c>
       <c r="S123" t="n">
-        <v>121.25</v>
+        <v>74.62</v>
       </c>
       <c r="T123" t="n">
-        <v>59.72</v>
+        <v>28.67</v>
       </c>
       <c r="U123" t="n">
-        <v>121.25</v>
+        <v>74.62</v>
       </c>
     </row>
     <row r="124">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="n">
@@ -8911,7 +8911,7 @@
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R124" t="inlineStr">
         <is>
@@ -8919,11 +8919,11 @@
         </is>
       </c>
       <c r="S124" t="n">
-        <v>6.25</v>
+        <v>3.85</v>
       </c>
       <c r="T124" t="inlineStr"/>
       <c r="U124" t="n">
-        <v>6.25</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="125">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M125" t="n">
         <v>58.9</v>
@@ -8982,7 +8982,7 @@
         <v>17148.7</v>
       </c>
       <c r="Q125" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R125" t="inlineStr">
         <is>
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="S125" t="n">
-        <v>116.67</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="T125" t="n">
-        <v>142.91</v>
+        <v>68.59</v>
       </c>
       <c r="U125" t="n">
-        <v>142.91</v>
+        <v>71.79000000000001</v>
       </c>
     </row>
     <row r="126">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="n">
@@ -9049,7 +9049,7 @@
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R126" t="inlineStr">
         <is>
@@ -9057,11 +9057,11 @@
         </is>
       </c>
       <c r="S126" t="n">
-        <v>556.25</v>
+        <v>342.31</v>
       </c>
       <c r="T126" t="inlineStr"/>
       <c r="U126" t="n">
-        <v>556.25</v>
+        <v>342.31</v>
       </c>
     </row>
     <row r="127">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="n">
@@ -9114,7 +9114,7 @@
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R127" t="inlineStr">
         <is>
@@ -9122,11 +9122,11 @@
         </is>
       </c>
       <c r="S127" t="n">
-        <v>993.75</v>
+        <v>611.54</v>
       </c>
       <c r="T127" t="inlineStr"/>
       <c r="U127" t="n">
-        <v>993.75</v>
+        <v>611.54</v>
       </c>
     </row>
     <row r="128">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M128" t="n">
         <v>55.7</v>
@@ -9185,7 +9185,7 @@
         <v>7685.8</v>
       </c>
       <c r="Q128" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R128" t="inlineStr">
         <is>
@@ -9193,13 +9193,13 @@
         </is>
       </c>
       <c r="S128" t="n">
-        <v>110.42</v>
+        <v>67.95</v>
       </c>
       <c r="T128" t="n">
-        <v>64.05</v>
+        <v>30.74</v>
       </c>
       <c r="U128" t="n">
-        <v>110.42</v>
+        <v>67.95</v>
       </c>
     </row>
     <row r="129">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M129" t="n">
         <v>38.9</v>
@@ -9258,7 +9258,7 @@
         <v>5968.6</v>
       </c>
       <c r="Q129" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R129" t="inlineStr">
         <is>
@@ -9266,13 +9266,13 @@
         </is>
       </c>
       <c r="S129" t="n">
-        <v>77.08</v>
+        <v>47.44</v>
       </c>
       <c r="T129" t="n">
-        <v>49.74</v>
+        <v>23.87</v>
       </c>
       <c r="U129" t="n">
-        <v>77.08</v>
+        <v>47.44</v>
       </c>
     </row>
     <row r="130">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M130" t="n">
         <v>114.6</v>
@@ -9331,7 +9331,7 @@
         <v>7427.2</v>
       </c>
       <c r="Q130" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R130" t="inlineStr">
         <is>
@@ -9339,13 +9339,13 @@
         </is>
       </c>
       <c r="S130" t="n">
-        <v>227.08</v>
+        <v>139.74</v>
       </c>
       <c r="T130" t="n">
-        <v>61.89</v>
+        <v>29.71</v>
       </c>
       <c r="U130" t="n">
-        <v>227.08</v>
+        <v>139.74</v>
       </c>
     </row>
     <row r="131">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M131" t="n">
         <v>100.9</v>
@@ -9404,7 +9404,7 @@
         <v>10602.1</v>
       </c>
       <c r="Q131" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R131" t="inlineStr">
         <is>
@@ -9412,13 +9412,13 @@
         </is>
       </c>
       <c r="S131" t="n">
-        <v>200</v>
+        <v>123.08</v>
       </c>
       <c r="T131" t="n">
-        <v>88.34999999999999</v>
+        <v>42.41</v>
       </c>
       <c r="U131" t="n">
-        <v>200</v>
+        <v>123.08</v>
       </c>
     </row>
     <row r="132">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M132" t="n">
         <v>51.5</v>
@@ -9477,7 +9477,7 @@
         <v>12495.4</v>
       </c>
       <c r="Q132" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R132" t="inlineStr">
         <is>
@@ -9485,13 +9485,13 @@
         </is>
       </c>
       <c r="S132" t="n">
-        <v>102.08</v>
+        <v>62.82</v>
       </c>
       <c r="T132" t="n">
-        <v>104.13</v>
+        <v>49.98</v>
       </c>
       <c r="U132" t="n">
-        <v>104.13</v>
+        <v>62.82</v>
       </c>
     </row>
     <row r="133">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M133" t="n">
         <v>2.1</v>
@@ -9550,7 +9550,7 @@
         <v>430</v>
       </c>
       <c r="Q133" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R133" t="inlineStr">
         <is>
@@ -9558,13 +9558,13 @@
         </is>
       </c>
       <c r="S133" t="n">
-        <v>4.17</v>
+        <v>2.56</v>
       </c>
       <c r="T133" t="n">
-        <v>3.58</v>
+        <v>1.72</v>
       </c>
       <c r="U133" t="n">
-        <v>4.17</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="134">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M134" t="n">
         <v>92.5</v>
@@ -9623,7 +9623,7 @@
         <v>23686.2</v>
       </c>
       <c r="Q134" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R134" t="inlineStr">
         <is>
@@ -9631,13 +9631,13 @@
         </is>
       </c>
       <c r="S134" t="n">
-        <v>183.33</v>
+        <v>112.82</v>
       </c>
       <c r="T134" t="n">
-        <v>197.39</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="U134" t="n">
-        <v>197.39</v>
+        <v>112.82</v>
       </c>
     </row>
     <row r="135">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M135" t="n">
         <v>6.3</v>
@@ -9696,7 +9696,7 @@
         <v>1842.5</v>
       </c>
       <c r="Q135" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R135" t="inlineStr">
         <is>
@@ -9704,13 +9704,13 @@
         </is>
       </c>
       <c r="S135" t="n">
-        <v>12.5</v>
+        <v>7.69</v>
       </c>
       <c r="T135" t="n">
-        <v>15.35</v>
+        <v>7.37</v>
       </c>
       <c r="U135" t="n">
-        <v>15.35</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="136">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M136" t="n">
         <v>50.6</v>
@@ -9769,7 +9769,7 @@
         <v>6712.5</v>
       </c>
       <c r="Q136" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R136" t="inlineStr">
         <is>
@@ -9777,13 +9777,13 @@
         </is>
       </c>
       <c r="S136" t="n">
-        <v>113.59</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="T136" t="n">
-        <v>55.94</v>
+        <v>26.85</v>
       </c>
       <c r="U136" t="n">
-        <v>113.59</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="137">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="n">
@@ -9838,7 +9838,7 @@
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R137" t="inlineStr">
         <is>
@@ -9846,11 +9846,11 @@
         </is>
       </c>
       <c r="S137" t="n">
-        <v>6.25</v>
+        <v>3.85</v>
       </c>
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="n">
-        <v>6.25</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="138">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M138" t="n">
         <v>65.2</v>
@@ -9909,7 +9909,7 @@
         <v>19018</v>
       </c>
       <c r="Q138" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R138" t="inlineStr">
         <is>
@@ -9917,13 +9917,13 @@
         </is>
       </c>
       <c r="S138" t="n">
-        <v>129.17</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="T138" t="n">
-        <v>158.48</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="U138" t="n">
-        <v>158.48</v>
+        <v>79.48999999999999</v>
       </c>
     </row>
     <row r="139">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M139" t="n">
         <v>34.7</v>
@@ -9982,7 +9982,7 @@
         <v>6384</v>
       </c>
       <c r="Q139" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R139" t="inlineStr">
         <is>
@@ -9990,13 +9990,13 @@
         </is>
       </c>
       <c r="S139" t="n">
-        <v>68.75</v>
+        <v>42.31</v>
       </c>
       <c r="T139" t="n">
-        <v>53.2</v>
+        <v>25.54</v>
       </c>
       <c r="U139" t="n">
-        <v>68.75</v>
+        <v>42.31</v>
       </c>
     </row>
     <row r="140">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="n">
@@ -10049,7 +10049,7 @@
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R140" t="inlineStr">
         <is>
@@ -10057,11 +10057,11 @@
         </is>
       </c>
       <c r="S140" t="n">
-        <v>650</v>
+        <v>400</v>
       </c>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="n">
-        <v>650</v>
+        <v>400</v>
       </c>
     </row>
     <row r="141">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="n">
@@ -10114,7 +10114,7 @@
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R141" t="inlineStr">
         <is>
@@ -10122,11 +10122,11 @@
         </is>
       </c>
       <c r="S141" t="n">
-        <v>881.25</v>
+        <v>542.3099999999999</v>
       </c>
       <c r="T141" t="inlineStr"/>
       <c r="U141" t="n">
-        <v>881.25</v>
+        <v>542.3099999999999</v>
       </c>
     </row>
     <row r="142">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M142" t="n">
         <v>17.9</v>
@@ -10185,7 +10185,7 @@
         <v>2410.4</v>
       </c>
       <c r="Q142" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R142" t="inlineStr">
         <is>
@@ -10193,13 +10193,13 @@
         </is>
       </c>
       <c r="S142" t="n">
-        <v>35.42</v>
+        <v>21.79</v>
       </c>
       <c r="T142" t="n">
-        <v>20.09</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="U142" t="n">
-        <v>35.42</v>
+        <v>21.79</v>
       </c>
     </row>
     <row r="143">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M143" t="n">
         <v>44.1</v>
@@ -10258,7 +10258,7 @@
         <v>6858.7</v>
       </c>
       <c r="Q143" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R143" t="inlineStr">
         <is>
@@ -10266,13 +10266,13 @@
         </is>
       </c>
       <c r="S143" t="n">
-        <v>87.5</v>
+        <v>53.85</v>
       </c>
       <c r="T143" t="n">
-        <v>57.16</v>
+        <v>27.43</v>
       </c>
       <c r="U143" t="n">
-        <v>87.5</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="144">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M144" t="n">
         <v>35.7</v>
@@ -10331,7 +10331,7 @@
         <v>2316.8</v>
       </c>
       <c r="Q144" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R144" t="inlineStr">
         <is>
@@ -10339,13 +10339,13 @@
         </is>
       </c>
       <c r="S144" t="n">
-        <v>70.83</v>
+        <v>43.59</v>
       </c>
       <c r="T144" t="n">
-        <v>19.31</v>
+        <v>9.27</v>
       </c>
       <c r="U144" t="n">
-        <v>70.83</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="145">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M145" t="n">
         <v>105.1</v>
@@ -10404,7 +10404,7 @@
         <v>11049.1</v>
       </c>
       <c r="Q145" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R145" t="inlineStr">
         <is>
@@ -10412,13 +10412,13 @@
         </is>
       </c>
       <c r="S145" t="n">
-        <v>208.33</v>
+        <v>128.21</v>
       </c>
       <c r="T145" t="n">
-        <v>92.08</v>
+        <v>44.2</v>
       </c>
       <c r="U145" t="n">
-        <v>208.33</v>
+        <v>128.21</v>
       </c>
     </row>
     <row r="146">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M146" t="n">
         <v>36.8</v>
@@ -10477,7 +10477,7 @@
         <v>8773.4</v>
       </c>
       <c r="Q146" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R146" t="inlineStr">
         <is>
@@ -10485,13 +10485,13 @@
         </is>
       </c>
       <c r="S146" t="n">
-        <v>72.92</v>
+        <v>44.87</v>
       </c>
       <c r="T146" t="n">
-        <v>73.11</v>
+        <v>35.09</v>
       </c>
       <c r="U146" t="n">
-        <v>73.11</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="147">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M147" t="n">
         <v>83</v>
@@ -10550,7 +10550,7 @@
         <v>21134.3</v>
       </c>
       <c r="Q147" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R147" t="inlineStr">
         <is>
@@ -10558,13 +10558,13 @@
         </is>
       </c>
       <c r="S147" t="n">
-        <v>164.58</v>
+        <v>101.28</v>
       </c>
       <c r="T147" t="n">
-        <v>176.12</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="U147" t="n">
-        <v>176.12</v>
+        <v>101.28</v>
       </c>
     </row>
     <row r="148">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M148" t="n">
         <v>8.4</v>
@@ -10623,7 +10623,7 @@
         <v>2325.2</v>
       </c>
       <c r="Q148" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R148" t="inlineStr">
         <is>
@@ -10631,13 +10631,13 @@
         </is>
       </c>
       <c r="S148" t="n">
-        <v>16.67</v>
+        <v>10.26</v>
       </c>
       <c r="T148" t="n">
-        <v>19.38</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="U148" t="n">
-        <v>19.38</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="149">
@@ -10667,14 +10667,14 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R149" t="inlineStr">
         <is>
@@ -10712,14 +10712,14 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R150" t="inlineStr">
         <is>
@@ -10757,14 +10757,14 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R151" t="inlineStr">
         <is>
@@ -10802,14 +10802,14 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R152" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
       </c>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M153" t="n">
         <v>40.5</v>
@@ -10876,7 +10876,7 @@
         <v>5372.1</v>
       </c>
       <c r="Q153" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R153" t="inlineStr">
         <is>
@@ -10884,13 +10884,13 @@
         </is>
       </c>
       <c r="S153" t="n">
-        <v>90.94</v>
+        <v>55.96</v>
       </c>
       <c r="T153" t="n">
-        <v>44.77</v>
+        <v>21.49</v>
       </c>
       <c r="U153" t="n">
-        <v>90.94</v>
+        <v>55.96</v>
       </c>
     </row>
     <row r="154">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="n">
@@ -10945,7 +10945,7 @@
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R154" t="inlineStr">
         <is>
@@ -10953,11 +10953,11 @@
         </is>
       </c>
       <c r="S154" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="155">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M155" t="n">
         <v>49.4</v>
@@ -11016,7 +11016,7 @@
         <v>14531.5</v>
       </c>
       <c r="Q155" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R155" t="inlineStr">
         <is>
@@ -11024,13 +11024,13 @@
         </is>
       </c>
       <c r="S155" t="n">
-        <v>97.92</v>
+        <v>60.26</v>
       </c>
       <c r="T155" t="n">
-        <v>121.1</v>
+        <v>58.13</v>
       </c>
       <c r="U155" t="n">
-        <v>121.1</v>
+        <v>60.26</v>
       </c>
     </row>
     <row r="156">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M156" t="n">
         <v>18.9</v>
@@ -11089,7 +11089,7 @@
         <v>3397.6</v>
       </c>
       <c r="Q156" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R156" t="inlineStr">
         <is>
@@ -11097,13 +11097,13 @@
         </is>
       </c>
       <c r="S156" t="n">
-        <v>37.5</v>
+        <v>23.08</v>
       </c>
       <c r="T156" t="n">
-        <v>28.31</v>
+        <v>13.59</v>
       </c>
       <c r="U156" t="n">
-        <v>37.5</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="157">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="n">
@@ -11156,7 +11156,7 @@
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R157" t="inlineStr">
         <is>
@@ -11164,11 +11164,11 @@
         </is>
       </c>
       <c r="S157" t="n">
-        <v>543.75</v>
+        <v>334.62</v>
       </c>
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="n">
-        <v>543.75</v>
+        <v>334.62</v>
       </c>
     </row>
     <row r="158">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="n">
@@ -11221,7 +11221,7 @@
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R158" t="inlineStr">
         <is>
@@ -11229,11 +11229,11 @@
         </is>
       </c>
       <c r="S158" t="n">
-        <v>806.25</v>
+        <v>496.15</v>
       </c>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="n">
-        <v>806.25</v>
+        <v>496.15</v>
       </c>
     </row>
     <row r="159">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M159" t="n">
         <v>23.1</v>
@@ -11292,7 +11292,7 @@
         <v>3163.7</v>
       </c>
       <c r="Q159" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R159" t="inlineStr">
         <is>
@@ -11300,13 +11300,13 @@
         </is>
       </c>
       <c r="S159" t="n">
-        <v>45.83</v>
+        <v>28.21</v>
       </c>
       <c r="T159" t="n">
-        <v>26.36</v>
+        <v>12.65</v>
       </c>
       <c r="U159" t="n">
-        <v>45.83</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="160">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M160" t="n">
         <v>35.7</v>
@@ -11365,7 +11365,7 @@
         <v>5543.5</v>
       </c>
       <c r="Q160" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R160" t="inlineStr">
         <is>
@@ -11373,13 +11373,13 @@
         </is>
       </c>
       <c r="S160" t="n">
-        <v>70.83</v>
+        <v>43.59</v>
       </c>
       <c r="T160" t="n">
-        <v>46.2</v>
+        <v>22.17</v>
       </c>
       <c r="U160" t="n">
-        <v>70.83</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="161">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M161" t="n">
         <v>45.2</v>
@@ -11438,7 +11438,7 @@
         <v>2929.9</v>
       </c>
       <c r="Q161" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R161" t="inlineStr">
         <is>
@@ -11446,13 +11446,13 @@
         </is>
       </c>
       <c r="S161" t="n">
-        <v>89.58</v>
+        <v>55.13</v>
       </c>
       <c r="T161" t="n">
-        <v>24.42</v>
+        <v>11.72</v>
       </c>
       <c r="U161" t="n">
-        <v>89.58</v>
+        <v>55.13</v>
       </c>
     </row>
     <row r="162">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M162" t="n">
         <v>89.3</v>
@@ -11511,7 +11511,7 @@
         <v>9400.6</v>
       </c>
       <c r="Q162" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R162" t="inlineStr">
         <is>
@@ -11519,13 +11519,13 @@
         </is>
       </c>
       <c r="S162" t="n">
-        <v>177.08</v>
+        <v>108.97</v>
       </c>
       <c r="T162" t="n">
-        <v>78.34</v>
+        <v>37.6</v>
       </c>
       <c r="U162" t="n">
-        <v>177.08</v>
+        <v>108.97</v>
       </c>
     </row>
     <row r="163">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M163" t="n">
         <v>37.8</v>
@@ -11584,7 +11584,7 @@
         <v>9119.6</v>
       </c>
       <c r="Q163" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R163" t="inlineStr">
         <is>
@@ -11592,13 +11592,13 @@
         </is>
       </c>
       <c r="S163" t="n">
-        <v>75</v>
+        <v>46.15</v>
       </c>
       <c r="T163" t="n">
-        <v>76</v>
+        <v>36.48</v>
       </c>
       <c r="U163" t="n">
-        <v>76</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="164">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M164" t="n">
         <v>75.7</v>
@@ -11657,7 +11657,7 @@
         <v>19234.2</v>
       </c>
       <c r="Q164" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R164" t="inlineStr">
         <is>
@@ -11665,13 +11665,13 @@
         </is>
       </c>
       <c r="S164" t="n">
-        <v>150</v>
+        <v>92.31</v>
       </c>
       <c r="T164" t="n">
-        <v>160.29</v>
+        <v>76.94</v>
       </c>
       <c r="U164" t="n">
-        <v>160.29</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="165">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M165" t="n">
         <v>5.3</v>
@@ -11730,7 +11730,7 @@
         <v>1322.6</v>
       </c>
       <c r="Q165" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R165" t="inlineStr">
         <is>
@@ -11738,13 +11738,13 @@
         </is>
       </c>
       <c r="S165" t="n">
-        <v>10.42</v>
+        <v>6.41</v>
       </c>
       <c r="T165" t="n">
-        <v>11.02</v>
+        <v>5.29</v>
       </c>
       <c r="U165" t="n">
-        <v>11.02</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="166">
@@ -11774,14 +11774,14 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R166" t="inlineStr">
         <is>
@@ -11819,14 +11819,14 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R167" t="inlineStr">
         <is>
@@ -11864,14 +11864,14 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R168" t="inlineStr">
         <is>
@@ -11909,14 +11909,14 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
       <c r="Q169" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R169" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
       </c>
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M170" t="n">
         <v>25</v>
@@ -11983,7 +11983,7 @@
         <v>3312.8</v>
       </c>
       <c r="Q170" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R170" t="inlineStr">
         <is>
@@ -11991,13 +11991,13 @@
         </is>
       </c>
       <c r="S170" t="n">
-        <v>56.09</v>
+        <v>34.52</v>
       </c>
       <c r="T170" t="n">
-        <v>27.61</v>
+        <v>13.25</v>
       </c>
       <c r="U170" t="n">
-        <v>56.09</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="171">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="n">
@@ -12052,7 +12052,7 @@
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R171" t="inlineStr">
         <is>
@@ -12060,11 +12060,11 @@
         </is>
       </c>
       <c r="S171" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
       <c r="T171" t="inlineStr"/>
       <c r="U171" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="172">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M172" t="n">
         <v>37.8</v>
@@ -12123,7 +12123,7 @@
         <v>11114</v>
       </c>
       <c r="Q172" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R172" t="inlineStr">
         <is>
@@ -12131,13 +12131,13 @@
         </is>
       </c>
       <c r="S172" t="n">
-        <v>75</v>
+        <v>46.15</v>
       </c>
       <c r="T172" t="n">
-        <v>92.62</v>
+        <v>44.46</v>
       </c>
       <c r="U172" t="n">
-        <v>92.62</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="173">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M173" t="n">
         <v>9.5</v>
@@ -12196,7 +12196,7 @@
         <v>1755.2</v>
       </c>
       <c r="Q173" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R173" t="inlineStr">
         <is>
@@ -12204,13 +12204,13 @@
         </is>
       </c>
       <c r="S173" t="n">
-        <v>18.75</v>
+        <v>11.54</v>
       </c>
       <c r="T173" t="n">
-        <v>14.63</v>
+        <v>7.02</v>
       </c>
       <c r="U173" t="n">
-        <v>18.75</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="174">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="n">
@@ -12263,7 +12263,7 @@
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R174" t="inlineStr">
         <is>
@@ -12271,11 +12271,11 @@
         </is>
       </c>
       <c r="S174" t="n">
-        <v>537.5</v>
+        <v>330.77</v>
       </c>
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="n">
-        <v>537.5</v>
+        <v>330.77</v>
       </c>
     </row>
     <row r="175">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="n">
@@ -12328,7 +12328,7 @@
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R175" t="inlineStr">
         <is>
@@ -12336,11 +12336,11 @@
         </is>
       </c>
       <c r="S175" t="n">
-        <v>812.5</v>
+        <v>500</v>
       </c>
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="n">
-        <v>812.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="176">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M176" t="n">
         <v>31.5</v>
@@ -12399,7 +12399,7 @@
         <v>4290</v>
       </c>
       <c r="Q176" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R176" t="inlineStr">
         <is>
@@ -12407,13 +12407,13 @@
         </is>
       </c>
       <c r="S176" t="n">
-        <v>62.5</v>
+        <v>38.46</v>
       </c>
       <c r="T176" t="n">
-        <v>35.75</v>
+        <v>17.16</v>
       </c>
       <c r="U176" t="n">
-        <v>62.5</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="177">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M177" t="n">
         <v>35.7</v>
@@ -12472,7 +12472,7 @@
         <v>5545.9</v>
       </c>
       <c r="Q177" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R177" t="inlineStr">
         <is>
@@ -12480,13 +12480,13 @@
         </is>
       </c>
       <c r="S177" t="n">
-        <v>70.83</v>
+        <v>43.59</v>
       </c>
       <c r="T177" t="n">
-        <v>46.22</v>
+        <v>22.18</v>
       </c>
       <c r="U177" t="n">
-        <v>70.83</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="178">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M178" t="n">
         <v>65.2</v>
@@ -12545,7 +12545,7 @@
         <v>4224.6</v>
       </c>
       <c r="Q178" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R178" t="inlineStr">
         <is>
@@ -12553,13 +12553,13 @@
         </is>
       </c>
       <c r="S178" t="n">
-        <v>129.17</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="T178" t="n">
-        <v>35.21</v>
+        <v>16.9</v>
       </c>
       <c r="U178" t="n">
-        <v>129.17</v>
+        <v>79.48999999999999</v>
       </c>
     </row>
     <row r="179">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M179" t="n">
         <v>87.2</v>
@@ -12618,7 +12618,7 @@
         <v>9194.200000000001</v>
       </c>
       <c r="Q179" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R179" t="inlineStr">
         <is>
@@ -12626,13 +12626,13 @@
         </is>
       </c>
       <c r="S179" t="n">
-        <v>172.92</v>
+        <v>106.41</v>
       </c>
       <c r="T179" t="n">
-        <v>76.62</v>
+        <v>36.78</v>
       </c>
       <c r="U179" t="n">
-        <v>172.92</v>
+        <v>106.41</v>
       </c>
     </row>
     <row r="180">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M180" t="n">
         <v>43.1</v>
@@ -12691,7 +12691,7 @@
         <v>10433.6</v>
       </c>
       <c r="Q180" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R180" t="inlineStr">
         <is>
@@ -12699,13 +12699,13 @@
         </is>
       </c>
       <c r="S180" t="n">
-        <v>85.42</v>
+        <v>52.56</v>
       </c>
       <c r="T180" t="n">
-        <v>86.95</v>
+        <v>41.73</v>
       </c>
       <c r="U180" t="n">
-        <v>86.95</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="181">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M181" t="n">
         <v>75.7</v>
@@ -12764,7 +12764,7 @@
         <v>19382.6</v>
       </c>
       <c r="Q181" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R181" t="inlineStr">
         <is>
@@ -12772,13 +12772,13 @@
         </is>
       </c>
       <c r="S181" t="n">
-        <v>150</v>
+        <v>92.31</v>
       </c>
       <c r="T181" t="n">
-        <v>161.52</v>
+        <v>77.53</v>
       </c>
       <c r="U181" t="n">
-        <v>161.52</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="182">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M182" t="n">
         <v>5.3</v>
@@ -12837,7 +12837,7 @@
         <v>1393.3</v>
       </c>
       <c r="Q182" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R182" t="inlineStr">
         <is>
@@ -12845,13 +12845,13 @@
         </is>
       </c>
       <c r="S182" t="n">
-        <v>10.42</v>
+        <v>6.41</v>
       </c>
       <c r="T182" t="n">
-        <v>11.61</v>
+        <v>5.57</v>
       </c>
       <c r="U182" t="n">
-        <v>11.61</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="183">
@@ -12881,14 +12881,14 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
       <c r="Q183" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R183" t="inlineStr">
         <is>
@@ -12926,14 +12926,14 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
       <c r="Q184" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R184" t="inlineStr">
         <is>
@@ -12971,14 +12971,14 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
       <c r="Q185" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R185" t="inlineStr">
         <is>
@@ -13016,14 +13016,14 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="R186" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>4545</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -13182,13 +13182,13 @@
         <v>4545</v>
       </c>
       <c r="I2" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
-        <v>37875</v>
+        <v>10821.43</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -13201,10 +13201,10 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>94.6875</v>
+        <v>58.26923076923077</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.01282051282051282</v>
       </c>
     </row>
     <row r="3">
@@ -13223,7 +13223,7 @@
         <v>2494</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -13235,13 +13235,13 @@
         <v>2494</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>41566.67</v>
+        <v>17814.29</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -13254,10 +13254,10 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>155.875</v>
+        <v>95.92307692307692</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0625</v>
+        <v>0.03846153846153846</v>
       </c>
     </row>
     <row r="4">
@@ -13276,7 +13276,7 @@
         <v>7104</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -13288,13 +13288,13 @@
         <v>355.2</v>
       </c>
       <c r="I4" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>5920</v>
+        <v>1268.57</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -13307,10 +13307,10 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>11.1</v>
+        <v>6.83076923076923</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0015625</v>
+        <v>0.0009615384615384615</v>
       </c>
     </row>
     <row r="5">
@@ -13331,7 +13331,7 @@
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -13343,13 +13343,13 @@
         <v>14</v>
       </c>
       <c r="I5" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J5" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="K5" t="n">
-        <v>87.5</v>
+        <v>33.33</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -13362,10 +13362,10 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>0.4375</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03125</v>
+        <v>0.01923076923076923</v>
       </c>
     </row>
   </sheetData>

--- a/Viajante/VIAJANTE.xlsx
+++ b/Viajante/VIAJANTE.xlsx
@@ -579,15 +579,15 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -652,15 +652,15 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -719,15 +719,15 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -792,15 +792,15 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -857,15 +857,15 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -922,15 +922,15 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -995,15 +995,15 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1068,15 +1068,15 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1141,15 +1141,15 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1214,15 +1214,15 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1287,15 +1287,15 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1360,15 +1360,15 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1433,15 +1433,15 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1506,15 +1506,15 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1579,15 +1579,15 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1646,15 +1646,15 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1719,15 +1719,15 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1792,15 +1792,15 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1857,15 +1857,15 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1922,15 +1922,15 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1995,15 +1995,15 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2068,15 +2068,15 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2141,15 +2141,15 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2214,15 +2214,15 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2287,15 +2287,15 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2360,15 +2360,15 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2433,15 +2433,15 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2506,15 +2506,15 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2551,15 +2551,15 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2596,15 +2596,15 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2669,15 +2669,15 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2736,15 +2736,15 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2809,15 +2809,15 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2882,15 +2882,15 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2947,15 +2947,15 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3012,15 +3012,15 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3085,15 +3085,15 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3158,15 +3158,15 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3231,15 +3231,15 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3304,15 +3304,15 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3377,15 +3377,15 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3450,15 +3450,15 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3523,15 +3523,15 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3568,15 +3568,15 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3613,15 +3613,15 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3658,15 +3658,15 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3703,15 +3703,15 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3776,15 +3776,15 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3843,15 +3843,15 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3916,15 +3916,15 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3981,15 +3981,15 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4046,15 +4046,15 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4119,15 +4119,15 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4192,15 +4192,15 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4265,15 +4265,15 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4338,15 +4338,15 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4411,15 +4411,15 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4484,15 +4484,15 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4557,15 +4557,15 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4630,15 +4630,15 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4675,15 +4675,15 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4720,15 +4720,15 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4793,15 +4793,15 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4860,15 +4860,15 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4933,15 +4933,15 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5006,15 +5006,15 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5071,15 +5071,15 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5136,15 +5136,15 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5209,15 +5209,15 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5282,15 +5282,15 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5355,15 +5355,15 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5428,15 +5428,15 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5501,15 +5501,15 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5574,15 +5574,15 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5619,15 +5619,15 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5664,15 +5664,15 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5709,15 +5709,15 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5754,15 +5754,15 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5827,15 +5827,15 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5894,15 +5894,15 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5967,15 +5967,15 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6040,15 +6040,15 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6105,15 +6105,15 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6170,15 +6170,15 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6243,15 +6243,15 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6316,15 +6316,15 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6389,15 +6389,15 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6462,15 +6462,15 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6535,15 +6535,15 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6608,15 +6608,15 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6681,15 +6681,15 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6754,15 +6754,15 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6799,15 +6799,15 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6844,15 +6844,15 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6917,15 +6917,15 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6984,15 +6984,15 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7057,15 +7057,15 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7130,15 +7130,15 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7195,15 +7195,15 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7260,15 +7260,15 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7333,15 +7333,15 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7406,15 +7406,15 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7479,15 +7479,15 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7552,15 +7552,15 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7625,15 +7625,15 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7698,15 +7698,15 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7771,15 +7771,15 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7844,15 +7844,15 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7889,15 +7889,15 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7934,15 +7934,15 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8007,15 +8007,15 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8074,15 +8074,15 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8147,15 +8147,15 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8212,15 +8212,15 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8277,15 +8277,15 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8350,15 +8350,15 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8423,15 +8423,15 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8496,15 +8496,15 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8569,15 +8569,15 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8642,15 +8642,15 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8715,15 +8715,15 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8788,15 +8788,15 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8861,15 +8861,15 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8928,15 +8928,15 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9001,15 +9001,15 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9066,15 +9066,15 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9131,15 +9131,15 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9204,15 +9204,15 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9277,15 +9277,15 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9350,15 +9350,15 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9423,15 +9423,15 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9496,15 +9496,15 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9569,15 +9569,15 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9642,15 +9642,15 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9715,15 +9715,15 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9788,15 +9788,15 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9855,15 +9855,15 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9928,15 +9928,15 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10001,15 +10001,15 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10066,15 +10066,15 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10131,15 +10131,15 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10204,15 +10204,15 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10277,15 +10277,15 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10350,15 +10350,15 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10423,15 +10423,15 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10496,15 +10496,15 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10569,15 +10569,15 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10642,15 +10642,15 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10687,15 +10687,15 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10732,15 +10732,15 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10777,15 +10777,15 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10822,15 +10822,15 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10895,15 +10895,15 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10962,15 +10962,15 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11035,15 +11035,15 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11108,15 +11108,15 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11173,15 +11173,15 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11238,15 +11238,15 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11311,15 +11311,15 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11384,15 +11384,15 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11457,15 +11457,15 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11530,15 +11530,15 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11603,15 +11603,15 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11676,15 +11676,15 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11749,15 +11749,15 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11794,15 +11794,15 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11839,15 +11839,15 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11884,15 +11884,15 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11929,15 +11929,15 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12002,15 +12002,15 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12069,15 +12069,15 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12142,15 +12142,15 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12215,15 +12215,15 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12280,15 +12280,15 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12345,15 +12345,15 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12418,15 +12418,15 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12491,15 +12491,15 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12564,15 +12564,15 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12637,15 +12637,15 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12710,15 +12710,15 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12783,15 +12783,15 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12856,15 +12856,15 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12901,15 +12901,15 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12946,15 +12946,15 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12991,15 +12991,15 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13156,11 +13156,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -13209,11 +13209,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -13262,11 +13262,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -13315,11 +13315,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -13426,15 +13426,15 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -13444,15 +13444,15 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -13462,15 +13462,15 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -13480,15 +13480,15 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>800002588</v>
+        <v>800006503</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DANA II</t>
+          <t>COOPER STANDARD III</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
